--- a/data/trans_orig/P6711-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6711-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2012</t>
+          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9187</t>
+          <t>9325</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25081</t>
+          <t>24441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28155</t>
+          <t>27769</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24592</t>
+          <t>25427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46279</t>
+          <t>48278</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11643</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20231</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>11883</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27751</t>
+          <t>28680</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17099</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19687</t>
+          <t>19241</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39638</t>
+          <t>39185</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>8648</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25560</t>
+          <t>23423</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11786</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26895</t>
+          <t>26455</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24328</t>
+          <t>23654</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45131</t>
+          <t>45693</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>17901</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35764</t>
+          <t>35872</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23874</t>
+          <t>25121</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42723</t>
+          <t>43182</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48657</t>
+          <t>48579</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71897</t>
+          <t>73567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>43,11%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35174</t>
+          <t>35480</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60778</t>
+          <t>60689</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>22175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44991</t>
+          <t>44820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62569</t>
+          <t>63883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100011</t>
+          <t>99915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15620</t>
+          <t>15589</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34599</t>
+          <t>33795</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19082</t>
+          <t>19284</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40991</t>
+          <t>41114</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39401</t>
+          <t>39731</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71087</t>
+          <t>69388</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62466</t>
+          <t>61441</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95691</t>
+          <t>92797</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30999</t>
+          <t>30827</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53698</t>
+          <t>55205</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>98999</t>
+          <t>98150</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>139313</t>
+          <t>138669</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61478</t>
+          <t>61176</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91922</t>
+          <t>92071</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38310</t>
+          <t>38486</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63925</t>
+          <t>64586</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106900</t>
+          <t>107296</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146334</t>
+          <t>148612</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139317</t>
+          <t>141331</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>180352</t>
+          <t>180944</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>103386</t>
+          <t>105320</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>138081</t>
+          <t>138703</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>256414</t>
+          <t>255945</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>312540</t>
+          <t>308346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37172</t>
+          <t>36650</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64977</t>
+          <t>63648</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19418</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40070</t>
+          <t>40503</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60016</t>
+          <t>61048</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95200</t>
+          <t>96636</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27241</t>
+          <t>27223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51605</t>
+          <t>51208</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11805</t>
+          <t>11285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28297</t>
+          <t>29101</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44635</t>
+          <t>44168</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75878</t>
+          <t>72192</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54921</t>
+          <t>54732</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83785</t>
+          <t>85790</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39156</t>
+          <t>39521</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65489</t>
+          <t>65854</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>101714</t>
+          <t>100943</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>141260</t>
+          <t>139589</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53409</t>
+          <t>53203</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84841</t>
+          <t>84595</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42418</t>
+          <t>43458</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69761</t>
+          <t>73852</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>104255</t>
+          <t>105002</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>145638</t>
+          <t>146814</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179497</t>
+          <t>178137</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222843</t>
+          <t>221043</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>113385</t>
+          <t>116133</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>148949</t>
+          <t>148909</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>303716</t>
+          <t>305652</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>357993</t>
+          <t>359631</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,64%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21052</t>
+          <t>20876</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43882</t>
+          <t>41957</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31684</t>
+          <t>30346</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57296</t>
+          <t>57245</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58012</t>
+          <t>57151</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92434</t>
+          <t>93336</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8241</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>25116</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26769</t>
+          <t>27475</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>21586</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>47029</t>
+          <t>45693</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>59264</t>
+          <t>58092</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>93937</t>
+          <t>94455</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>15885</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37479</t>
+          <t>37742</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81184</t>
+          <t>81165</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>123804</t>
+          <t>122761</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61630</t>
+          <t>61493</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>93014</t>
+          <t>96756</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32203</t>
+          <t>32543</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58792</t>
+          <t>59175</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>102036</t>
+          <t>101793</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>142792</t>
+          <t>145033</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>147377</t>
+          <t>146699</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>187591</t>
+          <t>189646</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>79447</t>
+          <t>79535</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>112160</t>
+          <t>112130</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>239159</t>
+          <t>237094</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>291441</t>
+          <t>290048</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25750</t>
+          <t>25139</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15180</t>
+          <t>15721</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34891</t>
+          <t>34363</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>996</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>9018</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16982</t>
+          <t>16848</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>36418</t>
+          <t>36042</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18106</t>
+          <t>18224</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25082</t>
+          <t>25632</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>50073</t>
+          <t>49382</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17700</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>35396</t>
+          <t>37512</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>18194</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>26570</t>
+          <t>25468</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>49479</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>75033</t>
+          <t>74316</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>100540</t>
+          <t>99941</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>30740</t>
+          <t>30700</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>47315</t>
+          <t>48033</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>110334</t>
+          <t>111768</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>142268</t>
+          <t>142501</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,76%</t>
         </is>
       </c>
     </row>
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4254,97 +4254,97 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>135140</t>
+          <t>134363</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>187696</t>
+          <t>184469</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>109113</t>
+          <t>111018</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>151900</t>
+          <t>153924</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>261031</t>
+          <t>258775</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>324660</t>
+          <t>323970</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>67807</t>
+          <t>68569</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>104222</t>
+          <t>104647</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>57302</t>
+          <t>57123</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>92366</t>
+          <t>91915</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>135331</t>
+          <t>135989</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>183177</t>
+          <t>184591</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>237508</t>
+          <t>237444</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>297677</t>
+          <t>297501</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>117339</t>
+          <t>119944</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>163264</t>
+          <t>163678</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>369878</t>
+          <t>367005</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>444998</t>
+          <t>441440</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>234572</t>
+          <t>232702</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>293311</t>
+          <t>290776</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>157693</t>
+          <t>156259</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>208098</t>
+          <t>206109</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>405761</t>
+          <t>403035</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>481282</t>
+          <t>481335</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>609132</t>
+          <t>607701</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>687135</t>
+          <t>683056</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>388759</t>
+          <t>391257</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>456692</t>
+          <t>457061</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1017359</t>
+          <t>1017357</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1120068</t>
+          <t>1118798</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,34%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2016</t>
+          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21092</t>
+          <t>22277</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21956</t>
+          <t>21150</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>19195</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38020</t>
+          <t>38652</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7946</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>22126</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22010</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19444</t>
+          <t>18831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12423</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28713</t>
+          <t>28589</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13316</t>
+          <t>13936</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28723</t>
+          <t>28982</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30610</t>
+          <t>30334</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52676</t>
+          <t>51763</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23530</t>
+          <t>22744</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16705</t>
+          <t>16141</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33301</t>
+          <t>33135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28731</t>
+          <t>27442</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50752</t>
+          <t>49948</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25489</t>
+          <t>23833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12717</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27577</t>
+          <t>27609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26893</t>
+          <t>26417</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47670</t>
+          <t>48383</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47709</t>
+          <t>46156</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75916</t>
+          <t>74392</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34330</t>
+          <t>35124</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59051</t>
+          <t>59630</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88048</t>
+          <t>88147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123647</t>
+          <t>125781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41611</t>
+          <t>41320</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70032</t>
+          <t>69666</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38678</t>
+          <t>39171</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65311</t>
+          <t>64152</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87653</t>
+          <t>86528</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125169</t>
+          <t>124279</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55733</t>
+          <t>57060</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86468</t>
+          <t>85387</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49311</t>
+          <t>49006</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76567</t>
+          <t>75580</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112818</t>
+          <t>111389</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152927</t>
+          <t>150565</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64745</t>
+          <t>67261</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96676</t>
+          <t>99820</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48314</t>
+          <t>48021</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75708</t>
+          <t>74119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120224</t>
+          <t>123058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163176</t>
+          <t>164685</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62309</t>
+          <t>62888</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93999</t>
+          <t>94018</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43846</t>
+          <t>43654</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70437</t>
+          <t>71164</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>113495</t>
+          <t>114789</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153487</t>
+          <t>155632</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42447</t>
+          <t>43119</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70366</t>
+          <t>70561</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44107</t>
+          <t>44676</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70799</t>
+          <t>72325</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93869</t>
+          <t>94673</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134342</t>
+          <t>132627</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45049</t>
+          <t>44920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73447</t>
+          <t>74109</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>24701</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44528</t>
+          <t>45256</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74372</t>
+          <t>74460</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>110031</t>
+          <t>112237</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85503</t>
+          <t>87052</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>121440</t>
+          <t>122646</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66376</t>
+          <t>66575</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>97589</t>
+          <t>96464</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>159920</t>
+          <t>159072</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>208629</t>
+          <t>207318</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86825</t>
+          <t>88570</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>125864</t>
+          <t>126083</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44285</t>
+          <t>44917</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72267</t>
+          <t>71737</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>140676</t>
+          <t>141643</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>189065</t>
+          <t>188620</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>117172</t>
+          <t>117201</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>157753</t>
+          <t>155826</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72061</t>
+          <t>72247</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>103196</t>
+          <t>103541</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>199000</t>
+          <t>198554</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>250883</t>
+          <t>248708</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51022</t>
+          <t>49947</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>81869</t>
+          <t>80911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38741</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65839</t>
+          <t>64890</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95872</t>
+          <t>96345</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>136889</t>
+          <t>138820</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26647</t>
+          <t>26947</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52293</t>
+          <t>51115</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>20543</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41928</t>
+          <t>41691</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>52871</t>
+          <t>52846</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83982</t>
+          <t>84593</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>71752</t>
+          <t>72611</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>106790</t>
+          <t>106717</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>65646</t>
+          <t>64061</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>119502</t>
+          <t>118520</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>162855</t>
+          <t>161402</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72072</t>
+          <t>71610</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>107405</t>
+          <t>104766</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36402</t>
+          <t>37268</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62068</t>
+          <t>63753</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117164</t>
+          <t>115761</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>160461</t>
+          <t>159203</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>72827</t>
+          <t>73773</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>108352</t>
+          <t>106615</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49470</t>
+          <t>48496</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>77733</t>
+          <t>76966</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>130976</t>
+          <t>131284</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>174435</t>
+          <t>175234</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25892</t>
+          <t>23843</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>17792</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37854</t>
+          <t>37154</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>30155</t>
+          <t>31077</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56273</t>
+          <t>56205</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27655</t>
+          <t>28004</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25271</t>
+          <t>24158</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22536</t>
+          <t>23152</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>45952</t>
+          <t>46591</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>27627</t>
+          <t>27910</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>51651</t>
+          <t>51501</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13178</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30430</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>47638</t>
+          <t>45948</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>76640</t>
+          <t>75867</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20388</t>
+          <t>21247</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41498</t>
+          <t>41064</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24757</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>34249</t>
+          <t>34790</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>61784</t>
+          <t>60090</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>50544</t>
+          <t>51123</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>75996</t>
+          <t>76329</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>17844</t>
+          <t>16795</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>36477</t>
+          <t>37553</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>74436</t>
+          <t>75638</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>106487</t>
+          <t>107841</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,7%</t>
         </is>
       </c>
     </row>
@@ -9832,97 +9832,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9945,97 +9945,97 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>62,38%</t>
         </is>
       </c>
     </row>
@@ -10171,97 +10171,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>833</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -10514,97 +10514,97 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10627,97 +10627,97 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10740,97 +10740,97 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10853,97 +10853,97 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
           <t>795</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10966,97 +10966,97 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>183727</t>
+          <t>180100</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>242179</t>
+          <t>235194</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>169379</t>
+          <t>169877</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>218940</t>
+          <t>222754</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>368278</t>
+          <t>368181</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>440988</t>
+          <t>442030</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>159464</t>
+          <t>156051</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>211966</t>
+          <t>208373</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>123325</t>
+          <t>123760</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>167301</t>
+          <t>166296</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>297315</t>
+          <t>294506</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>360440</t>
+          <t>363564</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>289795</t>
+          <t>291182</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>355911</t>
+          <t>353689</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>210541</t>
+          <t>209020</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>263069</t>
+          <t>265192</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>517409</t>
+          <t>517369</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>604552</t>
+          <t>605584</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>287616</t>
+          <t>289026</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>352724</t>
+          <t>355224</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>183184</t>
+          <t>182198</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>234586</t>
+          <t>234512</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>488044</t>
+          <t>486726</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>570849</t>
+          <t>569846</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>352342</t>
+          <t>352818</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>421121</t>
+          <t>427127</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>227804</t>
+          <t>224737</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>282490</t>
+          <t>284553</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>595372</t>
+          <t>593646</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>689774</t>
+          <t>686868</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6711-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6711-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24441</t>
+          <t>24598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>12383</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27769</t>
+          <t>27932</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25427</t>
+          <t>24741</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48278</t>
+          <t>47802</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>11998</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>12533</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21165</t>
+          <t>20305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28680</t>
+          <t>28305</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>17035</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19241</t>
+          <t>19859</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39185</t>
+          <t>39688</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23423</t>
+          <t>24155</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11309</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26455</t>
+          <t>26631</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23654</t>
+          <t>24059</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45693</t>
+          <t>44469</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17901</t>
+          <t>19018</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35872</t>
+          <t>35801</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25121</t>
+          <t>23639</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43182</t>
+          <t>42512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48579</t>
+          <t>47348</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73567</t>
+          <t>73521</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35480</t>
+          <t>34516</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60689</t>
+          <t>60015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>22155</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44820</t>
+          <t>44416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63883</t>
+          <t>63374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99915</t>
+          <t>99002</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>15823</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33795</t>
+          <t>35506</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19284</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41114</t>
+          <t>42009</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39731</t>
+          <t>39343</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69388</t>
+          <t>68095</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61441</t>
+          <t>61217</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92797</t>
+          <t>93543</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30827</t>
+          <t>30747</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55205</t>
+          <t>55706</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>98150</t>
+          <t>98528</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>138669</t>
+          <t>140266</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61176</t>
+          <t>60690</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92071</t>
+          <t>91280</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38486</t>
+          <t>38336</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64586</t>
+          <t>64836</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107296</t>
+          <t>104183</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148612</t>
+          <t>146524</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141331</t>
+          <t>140316</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>180944</t>
+          <t>181518</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>105320</t>
+          <t>104340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>138703</t>
+          <t>138387</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>255945</t>
+          <t>254193</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>308346</t>
+          <t>307945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,82%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36650</t>
+          <t>36966</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63648</t>
+          <t>64294</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40503</t>
+          <t>39070</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61048</t>
+          <t>61212</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96636</t>
+          <t>95645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27223</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51208</t>
+          <t>52696</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11285</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29101</t>
+          <t>28883</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44168</t>
+          <t>44542</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72192</t>
+          <t>73578</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54732</t>
+          <t>54354</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85790</t>
+          <t>83886</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39521</t>
+          <t>40632</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65854</t>
+          <t>67918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>100943</t>
+          <t>99881</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>139589</t>
+          <t>137317</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53203</t>
+          <t>55081</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84595</t>
+          <t>84369</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43458</t>
+          <t>42938</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73852</t>
+          <t>70100</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>105002</t>
+          <t>103689</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>146814</t>
+          <t>146331</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>178137</t>
+          <t>180945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>221043</t>
+          <t>222746</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116133</t>
+          <t>112852</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>148909</t>
+          <t>147942</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>305652</t>
+          <t>307732</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>359631</t>
+          <t>360815</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,81%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20876</t>
+          <t>20906</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41957</t>
+          <t>42237</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>31089</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57245</t>
+          <t>57433</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57151</t>
+          <t>58148</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93336</t>
+          <t>92016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25116</t>
+          <t>25391</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>9677</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27475</t>
+          <t>26301</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45693</t>
+          <t>45589</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58092</t>
+          <t>60126</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>94455</t>
+          <t>96341</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37742</t>
+          <t>37731</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81165</t>
+          <t>81851</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>122761</t>
+          <t>122402</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61493</t>
+          <t>62698</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96756</t>
+          <t>95710</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32543</t>
+          <t>33235</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59175</t>
+          <t>60821</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>101793</t>
+          <t>102318</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>145033</t>
+          <t>143497</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>146699</t>
+          <t>147499</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>189646</t>
+          <t>188216</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>79535</t>
+          <t>78067</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>112130</t>
+          <t>109832</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>237094</t>
+          <t>238273</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>290048</t>
+          <t>291910</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25139</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14898</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15721</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34363</t>
+          <t>33538</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6398</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16848</t>
+          <t>15915</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>36042</t>
+          <t>36128</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18224</t>
+          <t>18070</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25632</t>
+          <t>24563</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>49382</t>
+          <t>48521</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18001</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37512</t>
+          <t>36073</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>18194</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>25468</t>
+          <t>26840</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>49218</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>74316</t>
+          <t>75021</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>99941</t>
+          <t>99358</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>30700</t>
+          <t>30941</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>48033</t>
+          <t>48585</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>111768</t>
+          <t>110893</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>142501</t>
+          <t>142292</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,67%</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>985</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>134363</t>
+          <t>135957</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>184469</t>
+          <t>182864</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>111018</t>
+          <t>109625</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>153924</t>
+          <t>154316</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>258775</t>
+          <t>260373</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>323970</t>
+          <t>323439</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>68569</t>
+          <t>68244</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>104647</t>
+          <t>104676</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>57123</t>
+          <t>58140</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>91915</t>
+          <t>92767</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>135989</t>
+          <t>136483</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>184591</t>
+          <t>184447</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>237444</t>
+          <t>235039</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>297501</t>
+          <t>296152</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>119944</t>
+          <t>119228</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>163678</t>
+          <t>166245</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>367005</t>
+          <t>370370</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>441440</t>
+          <t>447327</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>232702</t>
+          <t>232387</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>290776</t>
+          <t>291982</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>156259</t>
+          <t>159369</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>206109</t>
+          <t>209895</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>403035</t>
+          <t>406902</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>481335</t>
+          <t>482757</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>607701</t>
+          <t>605113</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>683056</t>
+          <t>686304</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>391257</t>
+          <t>391861</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>457061</t>
+          <t>454007</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1017357</t>
+          <t>1016766</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1118798</t>
+          <t>1120371</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,41%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>8565</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22277</t>
+          <t>22744</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7856</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21150</t>
+          <t>21729</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19195</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38652</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>7575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22126</t>
+          <t>21513</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22049</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18831</t>
+          <t>19087</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>12551</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28589</t>
+          <t>28676</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13936</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28982</t>
+          <t>28668</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>31031</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51763</t>
+          <t>52614</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22744</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16141</t>
+          <t>16686</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33135</t>
+          <t>33722</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27442</t>
+          <t>29678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49948</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23833</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12498</t>
+          <t>12598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27609</t>
+          <t>27288</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26417</t>
+          <t>26289</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48383</t>
+          <t>47413</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46156</t>
+          <t>46791</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74392</t>
+          <t>75726</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35124</t>
+          <t>34793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59630</t>
+          <t>58644</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88147</t>
+          <t>86352</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125781</t>
+          <t>123587</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41320</t>
+          <t>41128</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69666</t>
+          <t>69689</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39171</t>
+          <t>38986</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64152</t>
+          <t>63996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86528</t>
+          <t>87453</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124279</t>
+          <t>125223</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57060</t>
+          <t>56496</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85387</t>
+          <t>88066</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49006</t>
+          <t>48239</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75580</t>
+          <t>75867</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>111389</t>
+          <t>113212</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>150565</t>
+          <t>153172</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67261</t>
+          <t>66860</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99820</t>
+          <t>98020</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>47444</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74119</t>
+          <t>73315</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123058</t>
+          <t>121407</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164685</t>
+          <t>162833</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62888</t>
+          <t>64243</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94018</t>
+          <t>94485</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43654</t>
+          <t>43692</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71164</t>
+          <t>69876</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114789</t>
+          <t>114623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>155632</t>
+          <t>155078</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43119</t>
+          <t>41676</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70561</t>
+          <t>70410</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44676</t>
+          <t>44152</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72325</t>
+          <t>72414</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94673</t>
+          <t>93645</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132627</t>
+          <t>134331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44920</t>
+          <t>45419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74109</t>
+          <t>75467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24701</t>
+          <t>24812</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45256</t>
+          <t>45405</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74460</t>
+          <t>75719</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>112237</t>
+          <t>114819</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87052</t>
+          <t>86157</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>122646</t>
+          <t>122007</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66575</t>
+          <t>67854</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>96464</t>
+          <t>97775</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>159072</t>
+          <t>160287</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>207318</t>
+          <t>209408</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,95%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88570</t>
+          <t>88101</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>126083</t>
+          <t>125444</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44917</t>
+          <t>43641</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71737</t>
+          <t>70891</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>141643</t>
+          <t>142131</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>188620</t>
+          <t>186026</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>117201</t>
+          <t>117706</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155826</t>
+          <t>160687</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72247</t>
+          <t>72377</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>103541</t>
+          <t>104453</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>198554</t>
+          <t>196931</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>248708</t>
+          <t>250119</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49947</t>
+          <t>50347</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80911</t>
+          <t>81520</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38741</t>
+          <t>37585</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64890</t>
+          <t>64802</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96345</t>
+          <t>94066</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>138820</t>
+          <t>135291</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26947</t>
+          <t>26842</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51115</t>
+          <t>50152</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20543</t>
+          <t>21456</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41691</t>
+          <t>42614</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>52846</t>
+          <t>51584</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>84593</t>
+          <t>83329</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>72611</t>
+          <t>72630</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>106717</t>
+          <t>106945</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38079</t>
+          <t>38788</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64061</t>
+          <t>65014</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>118520</t>
+          <t>119354</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>161402</t>
+          <t>161961</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>71610</t>
+          <t>70452</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>104766</t>
+          <t>104016</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37268</t>
+          <t>36010</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63753</t>
+          <t>61795</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>115761</t>
+          <t>114917</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>159203</t>
+          <t>158593</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>73773</t>
+          <t>73919</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>106615</t>
+          <t>107968</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48496</t>
+          <t>50029</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>76966</t>
+          <t>77681</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>131284</t>
+          <t>129764</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>175234</t>
+          <t>174083</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8376</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23843</t>
+          <t>24171</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37154</t>
+          <t>38396</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31077</t>
+          <t>29470</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56205</t>
+          <t>56292</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28004</t>
+          <t>27598</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24158</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>23152</t>
+          <t>23165</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>46591</t>
+          <t>46307</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>27910</t>
+          <t>29252</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>51501</t>
+          <t>51788</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>31883</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>45948</t>
+          <t>48166</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>75867</t>
+          <t>76916</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21247</t>
+          <t>19797</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41064</t>
+          <t>40746</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24983</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>34790</t>
+          <t>33146</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>60090</t>
+          <t>59394</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>51123</t>
+          <t>50204</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>76329</t>
+          <t>76415</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16795</t>
+          <t>17628</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>37553</t>
+          <t>36541</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>75638</t>
+          <t>74779</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>107841</t>
+          <t>106869</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,35%</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,28%</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>180100</t>
+          <t>182424</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>235194</t>
+          <t>235679</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>169877</t>
+          <t>169161</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>222754</t>
+          <t>220399</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>368181</t>
+          <t>368616</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>442030</t>
+          <t>442263</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>156051</t>
+          <t>156323</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>208373</t>
+          <t>209598</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>123760</t>
+          <t>123466</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>166296</t>
+          <t>165940</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,47 +11359,47 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
+          <t>11,9%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>325816</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>293347</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>360650</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
           <t>11,93%</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>16,03%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>325816</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>294506</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>363564</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>13,25%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>291182</t>
+          <t>292172</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>353689</t>
+          <t>359023</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>209020</t>
+          <t>211917</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>265192</t>
+          <t>266281</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>517369</t>
+          <t>517766</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>605584</t>
+          <t>601500</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>289026</t>
+          <t>288436</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>355224</t>
+          <t>354467</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>182198</t>
+          <t>184257</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>234512</t>
+          <t>236757</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>486726</t>
+          <t>487394</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>569846</t>
+          <t>571347</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>352818</t>
+          <t>355631</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>427127</t>
+          <t>425663</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>224737</t>
+          <t>227784</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>284553</t>
+          <t>284347</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>593646</t>
+          <t>598049</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>686868</t>
+          <t>688615</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
